--- a/Templates/bulkImport/config/construct_RFI_config_sslr.xlsx
+++ b/Templates/bulkImport/config/construct_RFI_config_sslr.xlsx
@@ -1,20 +1,242 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9024"/>
+    <workbookView windowWidth="28800" windowHeight="12960"/>
   </bookViews>
   <sheets>
-    <sheet name="construct_RFI_config_sarawak" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="C5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">Date Format:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">2024-01-01
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">Date Format:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">2024-01-01
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">Date Format:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">2024-01-01
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S5" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t xml:space="preserve">Format : 12 Hours
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t xml:space="preserve">10:00 AM
+04:30 PM
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X5" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t xml:space="preserve">Format : 12 Hours
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t xml:space="preserve">10:00 AM
+04:30 PM
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Y5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">Date Format:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">2024-01-01
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AE5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">Date Format:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">2024-01-01
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AI5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">Date Format:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">2024-01-01
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="69">
   <si>
     <t>*</t>
   </si>
@@ -37,6 +259,9 @@
     <t>c_requested_by</t>
   </si>
   <si>
+    <t>c_site_doc_ref_no</t>
+  </si>
+  <si>
     <t>c_subject</t>
   </si>
   <si>
@@ -76,18 +301,6 @@
     <t>c_submitted_time</t>
   </si>
   <si>
-    <t>c_rfi_issue</t>
-  </si>
-  <si>
-    <t>c_issued_by</t>
-  </si>
-  <si>
-    <t>c_date_issued</t>
-  </si>
-  <si>
-    <t>c_issuer_remark</t>
-  </si>
-  <si>
     <t>c_rfi_acknowledge</t>
   </si>
   <si>
@@ -106,15 +319,15 @@
     <t>c_acknowledged_date</t>
   </si>
   <si>
+    <t>c_dcr</t>
+  </si>
+  <si>
     <t>c_response_desc</t>
   </si>
   <si>
     <t>c_response_file</t>
   </si>
   <si>
-    <t>c_dcr</t>
-  </si>
-  <si>
     <t>c_reviewed_by</t>
   </si>
   <si>
@@ -124,25 +337,108 @@
     <t>c_reviewed_date</t>
   </si>
   <si>
+    <t>c_rfi_acknowledge_response</t>
+  </si>
+  <si>
+    <t>c_acknowledge_response_by</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c_acknowledge_response_organization </t>
+  </si>
+  <si>
+    <t>c_acknowledge_response_date</t>
+  </si>
+  <si>
     <t>c_closed_remark</t>
   </si>
   <si>
     <t>Section</t>
   </si>
   <si>
-    <t>Work Discipline</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Reference No.</t>
-  </si>
-  <si>
-    <t>Requested By</t>
-  </si>
-  <si>
-    <t>Subject</t>
+    <t>Discipline</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Date </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>*</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Reference No. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>*</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Requested By </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>*</t>
+    </r>
+  </si>
+  <si>
+    <t>Site Document Reference No.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Subject </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>*</t>
+    </r>
   </si>
   <si>
     <t>Description</t>
@@ -166,7 +462,24 @@
     <t>Actioner</t>
   </si>
   <si>
-    <t>Action Date</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Action Date </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>*</t>
+    </r>
   </si>
   <si>
     <t>Status</t>
@@ -175,21 +488,29 @@
     <t>Submitted By</t>
   </si>
   <si>
-    <t>Submitted Date</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Submitted Date </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>*</t>
+    </r>
   </si>
   <si>
     <t>Submitted Time</t>
   </si>
   <si>
-    <t>Issue</t>
-  </si>
-  <si>
-    <t>Issued By</t>
-  </si>
-  <si>
-    <t>Issued Date</t>
-  </si>
-  <si>
     <t>Acknowledge</t>
   </si>
   <si>
@@ -205,7 +526,27 @@
     <t>Time</t>
   </si>
   <si>
-    <t>Design Change Request(DCR)</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Acknowledged Date </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>*</t>
+    </r>
+  </si>
+  <si>
+    <t>Design Change Request (DCR)</t>
   </si>
   <si>
     <t>Reviewed &amp; Approved By</t>
@@ -214,23 +555,66 @@
     <t>Organization</t>
   </si>
   <si>
-    <t>Date Reviewed</t>
-  </si>
-  <si>
-    <t>Closed Remarks</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Reviewed Date </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>*</t>
+    </r>
+  </si>
+  <si>
+    <t>Response Acknowledge By</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Acknowledge Response Date </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>*</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;RM&quot;* #,##0.00_-;\-&quot;RM&quot;* #,##0.00_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;RM&quot;* #,##0_-;\-&quot;RM&quot;* #,##0_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;₱&quot;* #,##0.00_-;\-&quot;₱&quot;* #,##0.00_-;_-&quot;₱&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;₱&quot;* #,##0_-;\-&quot;₱&quot;* #,##0_-;_-&quot;₱&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="26">
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+    </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -387,6 +771,30 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
     </font>
   </fonts>
   <fills count="33">
@@ -692,153 +1100,155 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1187,456 +1597,543 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AI5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4"/>
+  <dimension ref="A1:AJ5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="4"/>
   <cols>
-    <col min="12" max="14" width="21.8888888888889" customWidth="1"/>
-    <col min="15" max="15" width="15.1111111111111" customWidth="1"/>
-    <col min="16" max="16" width="16.7777777777778" customWidth="1"/>
-    <col min="17" max="17" width="17.5555555555556" customWidth="1"/>
-    <col min="18" max="19" width="18.5555555555556" customWidth="1"/>
+    <col min="1" max="1" width="12.2166666666667" customWidth="1"/>
+    <col min="2" max="2" width="16.775" customWidth="1"/>
+    <col min="3" max="3" width="19" customWidth="1"/>
+    <col min="4" max="4" width="16.2166666666667" customWidth="1"/>
+    <col min="5" max="5" width="16.775" customWidth="1"/>
+    <col min="6" max="7" width="13.8833333333333" customWidth="1"/>
+    <col min="8" max="8" width="15.1083333333333" customWidth="1"/>
+    <col min="9" max="9" width="17" customWidth="1"/>
+    <col min="10" max="10" width="14.8833333333333" customWidth="1"/>
+    <col min="14" max="17" width="15.775" customWidth="1"/>
+    <col min="18" max="19" width="17.4416666666667" customWidth="1"/>
+    <col min="20" max="21" width="18.5583333333333" customWidth="1"/>
+    <col min="22" max="22" width="23.4416666666667" customWidth="1"/>
+    <col min="23" max="23" width="24.4416666666667" customWidth="1"/>
+    <col min="24" max="24" width="22.5583333333333" customWidth="1"/>
+    <col min="25" max="25" width="21.6666666666667" customWidth="1"/>
+    <col min="26" max="28" width="16.8833333333333" customWidth="1"/>
+    <col min="29" max="29" width="23.775" customWidth="1"/>
+    <col min="30" max="31" width="16.8833333333333" customWidth="1"/>
+    <col min="32" max="32" width="26.8833333333333" customWidth="1"/>
+    <col min="33" max="33" width="27.4416666666667" customWidth="1"/>
+    <col min="34" max="34" width="35.775" customWidth="1"/>
+    <col min="35" max="35" width="31.775" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6">
-      <c r="B1" t="s">
+    <row r="1" ht="14.4" spans="1:35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" t="s">
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="F1" t="s">
+      <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
+      <c r="AC1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="2" spans="1:35">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2" t="s">
-        <v>1</v>
-      </c>
-      <c r="L2" t="s">
-        <v>1</v>
-      </c>
-      <c r="M2" t="s">
-        <v>1</v>
-      </c>
-      <c r="N2" t="s">
-        <v>1</v>
-      </c>
-      <c r="O2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R2" t="s">
-        <v>1</v>
-      </c>
-      <c r="S2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T2" t="s">
-        <v>1</v>
-      </c>
-      <c r="U2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V2" t="s">
-        <v>1</v>
-      </c>
-      <c r="W2" t="s">
-        <v>1</v>
-      </c>
-      <c r="X2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI2" t="s">
+    <row r="2" ht="14.4" spans="1:36">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:35">
-      <c r="A3">
+    <row r="3" ht="14.4" spans="1:36">
+      <c r="A3" s="1">
         <v>0</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1">
         <v>2</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>3</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>4</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>5</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>6</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>7</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <v>8</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="1">
         <v>9</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>10</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="1">
         <v>11</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="1">
         <v>12</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="1">
         <v>13</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="1">
         <v>14</v>
       </c>
-      <c r="P3">
+      <c r="P3" s="1">
         <v>15</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="1">
         <v>16</v>
       </c>
-      <c r="R3">
+      <c r="R3" s="1">
         <v>17</v>
       </c>
-      <c r="S3">
+      <c r="S3" s="1">
         <v>18</v>
       </c>
-      <c r="T3">
+      <c r="T3" s="1">
         <v>19</v>
       </c>
-      <c r="U3">
+      <c r="U3" s="1">
         <v>20</v>
       </c>
-      <c r="V3">
+      <c r="V3" s="1">
         <v>21</v>
       </c>
-      <c r="W3">
+      <c r="W3" s="1">
         <v>22</v>
       </c>
-      <c r="X3">
+      <c r="X3" s="1">
         <v>23</v>
       </c>
-      <c r="Y3">
+      <c r="Y3" s="1">
         <v>24</v>
       </c>
-      <c r="Z3">
+      <c r="Z3" s="1">
         <v>25</v>
       </c>
-      <c r="AA3">
+      <c r="AA3" s="1">
         <v>26</v>
       </c>
-      <c r="AB3">
+      <c r="AB3" s="1">
         <v>27</v>
       </c>
-      <c r="AC3">
+      <c r="AC3" s="1">
         <v>28</v>
       </c>
-      <c r="AD3">
+      <c r="AD3" s="1">
         <v>29</v>
       </c>
-      <c r="AE3">
+      <c r="AE3" s="1">
         <v>30</v>
       </c>
-      <c r="AF3">
+      <c r="AF3" s="1">
         <v>31</v>
       </c>
-      <c r="AG3">
+      <c r="AG3" s="1">
         <v>32</v>
       </c>
-      <c r="AH3">
+      <c r="AH3" s="1">
         <v>33</v>
       </c>
-      <c r="AI3">
+      <c r="AI3" s="1">
         <v>34</v>
       </c>
+      <c r="AJ3" s="1">
+        <v>35</v>
+      </c>
     </row>
-    <row r="4" spans="1:35">
-      <c r="A4" t="s">
+    <row r="4" ht="14.4" spans="1:36">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M4" t="s">
+      <c r="M4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N4" t="s">
+      <c r="N4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="O4" t="s">
+      <c r="O4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="P4" t="s">
+      <c r="P4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="Q4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="R4" t="s">
+      <c r="R4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="S4" t="s">
+      <c r="S4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="T4" t="s">
+      <c r="T4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="U4" t="s">
+      <c r="U4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="V4" t="s">
+      <c r="V4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="W4" t="s">
+      <c r="W4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="X4" t="s">
+      <c r="X4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Y4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="Z4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AA4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AB4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AC4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AD4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AE4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AF4" t="s">
+      <c r="AF4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AG4" t="s">
+      <c r="AG4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AH4" t="s">
+      <c r="AH4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AI4" t="s">
+      <c r="AI4" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="AJ4" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="5" spans="1:35">
-      <c r="A5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" t="s">
+    <row r="5" ht="14.4" spans="1:36">
+      <c r="A5" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B5" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D5" t="s">
+      <c r="C5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E5" t="s">
+      <c r="D5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F5" t="s">
+      <c r="E5" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G5" t="s">
+      <c r="F5" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H5" t="s">
+      <c r="G5" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="I5" t="s">
+      <c r="H5" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J5" t="s">
+      <c r="I5" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K5" t="s">
+      <c r="J5" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="L5" t="s">
+      <c r="K5" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="M5" t="s">
+      <c r="L5" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="N5" t="s">
+      <c r="M5" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="O5" t="s">
+      <c r="N5" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="P5" t="s">
+      <c r="O5" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="P5" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="R5" t="s">
+      <c r="Q5" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="S5" t="s">
+      <c r="R5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="T5" t="s">
+      <c r="S5" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="U5" t="s">
+      <c r="T5" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="V5" t="s">
+      <c r="U5" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="W5" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y5" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA5" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="W5" t="s">
-        <v>58</v>
-      </c>
-      <c r="X5" t="s">
-        <v>59</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>60</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>62</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AF5" t="s">
+      <c r="AB5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC5" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="AG5" t="s">
+      <c r="AD5" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="AH5" t="s">
+      <c r="AE5" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AI5" t="s">
+      <c r="AF5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AG5" s="1" t="s">
         <v>67</v>
+      </c>
+      <c r="AH5" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="AJ5" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1644,5 +2141,6 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>